--- a/data/naver_webtoon_series_mapping_duplicate_rows.xlsx
+++ b/data/naver_webtoon_series_mapping_duplicate_rows.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:19</t>
+          <t>2026-09-21 12:50:02</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -781,7 +781,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:19</t>
+          <t>2026-09-21 12:50:03</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:20</t>
+          <t>2026-09-21 12:50:03</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -1113,7 +1113,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:20</t>
+          <t>2026-09-21 12:50:03</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:20</t>
+          <t>2026-09-21 12:50:04</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:21</t>
+          <t>2026-09-21 12:50:04</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:22</t>
+          <t>2026-09-21 12:50:05</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:23</t>
+          <t>2026-09-21 12:50:06</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:23</t>
+          <t>2026-09-21 12:50:06</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:23</t>
+          <t>2026-09-21 12:50:06</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:23</t>
+          <t>2026-09-21 12:50:06</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -2390,7 +2390,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:24</t>
+          <t>2026-09-21 12:50:07</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -2556,7 +2556,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:24</t>
+          <t>2026-09-21 12:50:07</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:24</t>
+          <t>2026-09-21 12:50:07</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:24</t>
+          <t>2026-09-21 12:50:08</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:27</t>
+          <t>2026-09-21 12:50:10</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:27</t>
+          <t>2026-09-21 12:50:10</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:28</t>
+          <t>2026-09-21 12:50:11</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:28</t>
+          <t>2026-09-21 12:50:11</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:29</t>
+          <t>2026-09-21 12:50:11</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:29</t>
+          <t>2026-09-21 12:50:12</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -4001,7 +4001,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:30</t>
+          <t>2026-09-21 12:50:13</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:30</t>
+          <t>2026-09-21 12:50:13</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:31</t>
+          <t>2026-09-21 12:50:13</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:31</t>
+          <t>2026-09-21 12:50:14</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:32</t>
+          <t>2026-09-21 12:50:14</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:32</t>
+          <t>2026-09-21 12:50:14</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:32</t>
+          <t>2026-09-21 12:50:15</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:32</t>
+          <t>2026-09-21 12:50:15</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5270,7 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:34</t>
+          <t>2026-09-21 12:50:16</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:34</t>
+          <t>2026-09-21 12:50:16</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:34</t>
+          <t>2026-09-21 12:50:17</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -5758,7 +5758,7 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:34</t>
+          <t>2026-09-21 12:50:17</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:35</t>
+          <t>2026-09-21 12:50:17</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:35</t>
+          <t>2026-09-21 12:50:17</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:35</t>
+          <t>2026-09-21 12:50:17</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -6445,7 +6445,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:35</t>
+          <t>2026-09-21 12:50:17</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="AK38" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -6592,7 +6592,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:35</t>
+          <t>2026-09-21 12:50:17</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:38</t>
+          <t>2026-09-21 12:50:20</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -6928,7 +6928,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:38</t>
+          <t>2026-09-21 12:50:20</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -7078,7 +7078,7 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:38</t>
+          <t>2026-09-21 12:50:20</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:38</t>
+          <t>2026-09-21 12:50:20</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7445,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:38</t>
+          <t>2026-09-21 12:50:20</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="AK44" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -7592,7 +7592,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -7611,7 +7611,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:38</t>
+          <t>2026-09-21 12:50:20</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:39</t>
+          <t>2026-09-21 12:50:21</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:39</t>
+          <t>2026-09-21 12:50:21</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:41</t>
+          <t>2026-09-21 12:50:23</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:41</t>
+          <t>2026-09-21 12:50:23</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:41</t>
+          <t>2026-09-21 12:50:23</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:42</t>
+          <t>2026-09-21 12:50:23</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:42</t>
+          <t>2026-09-21 12:50:24</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -8910,7 +8910,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:43</t>
+          <t>2026-09-21 12:50:24</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-09-14 12:51:44</t>
+          <t>2026-09-21 12:50:25</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>2026-09-14 13:34:14</t>
+          <t>2026-09-21 13:34:37</t>
         </is>
       </c>
     </row>

--- a/data/naver_webtoon_series_mapping_duplicate_rows.xlsx
+++ b/data/naver_webtoon_series_mapping_duplicate_rows.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:33</t>
+          <t>2026-10-12 13:49:39</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -765,7 +765,7 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:33</t>
+          <t>2026-10-12 13:49:39</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -947,7 +947,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,7 +966,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:33</t>
+          <t>2026-10-12 13:49:40</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:34</t>
+          <t>2026-10-12 13:49:40</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -1230,7 +1230,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1249,7 +1249,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:34</t>
+          <t>2026-10-12 13:49:40</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:34</t>
+          <t>2026-10-12 13:49:40</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:36</t>
+          <t>2026-10-12 13:49:41</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:37</t>
+          <t>2026-10-12 13:49:42</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:37</t>
+          <t>2026-10-12 13:49:42</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -2077,7 +2077,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:37</t>
+          <t>2026-10-12 13:49:42</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -2224,7 +2224,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:37</t>
+          <t>2026-10-12 13:49:42</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -2390,31 +2390,31 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>브레이커즈</t>
+          <t>개집사</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=841810&amp;tab=tue</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=828292&amp;tab=tue</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>841810</t>
+          <t>828292</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:37</t>
+          <t>2026-10-12 13:49:43</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>JDL</t>
+          <t>고추참치</t>
         </is>
       </c>
       <c r="I13" t="b">
@@ -2445,21 +2445,21 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>브레이커즈</t>
+          <t>개집사</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>브레이커즈 (총 88화/미완결)</t>
+          <t>개집사 (총 203화/미완결)</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>총 88화/미완결</t>
+          <t>총 203화/미완결</t>
         </is>
       </c>
       <c r="R13" t="n">
-        <v>88</v>
+        <v>203</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -2468,21 +2468,187 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>평점 9.7 | JDL, 취룡 뚱또 | 2026.06.01. | 총88화/미완결 | 84화 무료</t>
+          <t>평점 10.0 | 고추참치 고추참치 | 2026.06.08. | 총203화/미완결 | 198화 무료</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="inlineStr">
         <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=11371316</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>11371316</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>개집사 (총 203화/미완결)
+평점
+10.0 | 고추참치 고추참치 | 2026.06.08. | 총203화/미완결 | 198화 무료
+출근도 퇴근도 없는 똑같은 일상의 작가…눈치채지 못한 사이 작가의 삶에 다이나믹한 소재를 주는 두 존재가 있었는데…! 작지만 자존감 만큼은 하늘 같은 말티즈, 덩칫값못하는 진도 믹스 아가씨들을 모시는 집사&amp;작가의 삶</t>
+        </is>
+      </c>
+      <c r="Y13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>145</v>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>title_contains,author_exact_or_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>first_non_compilation_numeric_download</t>
+        </is>
+      </c>
+      <c r="AE13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>59.2만</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>592000</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>tue</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>화</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>64</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>브레이커즈</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=841810&amp;tab=tue</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>841810</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026-10-12 13:49:43</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>JDL</t>
+        </is>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>화, 금 연재</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>tue,fri</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>tue,fri</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>1</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>브레이커즈</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>브레이커즈 (총 88화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>총 88화/미완결</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>88</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>평점 9.7 | JDL, 취룡 뚱또 | 2026.06.01. | 총88화/미완결 | 84화 무료</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr">
+        <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13011302</t>
         </is>
       </c>
-      <c r="W13" t="inlineStr">
+      <c r="W14" t="inlineStr">
         <is>
           <t>13011302</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>브레이커즈 (총 88화/미완결)
 평점
@@ -2490,172 +2656,6 @@
 '주인공'은 즐겨하던 게임의 리메이크판인 &lt;나이트 사가:re&gt;를 플레이하던 중,게임 속으로 끌려들어 간다.그런데 무언가 이상하다.&lt;나이트 사가:re&gt;에서 플레이어블 캐릭터는 인간 편의 로크, 마계 편의 제피르뿐.그러나 정신..</t>
         </is>
       </c>
-      <c r="Y13" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>145</v>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>title_contains,author_exact_or_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>matched</t>
-        </is>
-      </c>
-      <c r="AD13" t="inlineStr">
-        <is>
-          <t>first_non_compilation_numeric_download</t>
-        </is>
-      </c>
-      <c r="AE13" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>46.5만</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>465000</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>2026-10-05 14:23:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>tue</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>화</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>63</v>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>개집사</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=828292&amp;tab=tue</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>828292</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>2026-10-05 13:35:38</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>고추참치</t>
-        </is>
-      </c>
-      <c r="I14" t="b">
-        <v>0</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>화, 금 연재</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>tue,fri</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>tue,fri</t>
-        </is>
-      </c>
-      <c r="N14" t="n">
-        <v>1</v>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>개집사</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>개집사 (총 203화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>총 203화/미완결</t>
-        </is>
-      </c>
-      <c r="R14" t="n">
-        <v>203</v>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 고추참치 고추참치 | 2026.06.08. | 총203화/미완결 | 198화 무료</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=11371316</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>11371316</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>개집사 (총 203화/미완결)
-평점
-10.0 | 고추참치 고추참치 | 2026.06.08. | 총203화/미완결 | 198화 무료
-출근도 퇴근도 없는 똑같은 일상의 작가…눈치채지 못한 사이 작가의 삶에 다이나믹한 소재를 주는 두 존재가 있었는데…! 작지만 자존감 만큼은 하늘 같은 말티즈, 덩칫값못하는 진도 믹스 아가씨들을 모시는 집사&amp;작가의 삶</t>
-        </is>
-      </c>
       <c r="Y14" t="b">
         <v>0</v>
       </c>
@@ -2685,11 +2685,11 @@
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>59.2만</t>
+          <t>46.5만</t>
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>592000</v>
+        <v>465000</v>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -2722,7 +2722,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2741,7 +2741,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:38</t>
+          <t>2026-10-12 13:49:43</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -2888,7 +2888,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:38</t>
+          <t>2026-10-12 13:49:43</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:40</t>
+          <t>2026-10-12 13:49:44</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -3220,7 +3220,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:40</t>
+          <t>2026-10-12 13:49:45</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3405,7 +3405,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:40</t>
+          <t>2026-10-12 13:49:45</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3522,7 +3522,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:41</t>
+          <t>2026-10-12 13:49:45</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -3653,7 +3653,7 @@
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:41</t>
+          <t>2026-10-12 13:49:45</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3835,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3854,7 +3854,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:41</t>
+          <t>2026-10-12 13:49:45</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -4020,7 +4020,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:43</t>
+          <t>2026-10-12 13:49:46</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -4186,7 +4186,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:43</t>
+          <t>2026-10-12 13:49:47</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="AK24" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -4342,7 +4342,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:43</t>
+          <t>2026-10-12 13:49:47</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="AK25" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -4508,7 +4508,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:43</t>
+          <t>2026-10-12 13:49:47</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -4639,7 +4639,7 @@
       </c>
       <c r="AK26" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4655,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4674,7 +4674,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:44</t>
+          <t>2026-10-12 13:49:47</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="AK27" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:44</t>
+          <t>2026-10-12 13:49:48</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -4922,7 +4922,7 @@
       </c>
       <c r="AK28" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4938,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4957,7 +4957,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:44</t>
+          <t>2026-10-12 13:49:48</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="AK29" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -5104,7 +5104,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -5123,7 +5123,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:44</t>
+          <t>2026-10-12 13:49:48</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="AK30" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5289,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:46</t>
+          <t>2026-10-12 13:49:49</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="AK31" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:46</t>
+          <t>2026-10-12 13:49:49</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="AK32" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -5592,7 +5592,7 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -5611,7 +5611,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:47</t>
+          <t>2026-10-12 13:49:49</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -5742,7 +5742,7 @@
       </c>
       <c r="AK33" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:47</t>
+          <t>2026-10-12 13:49:49</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -5912,7 +5912,7 @@
       </c>
       <c r="AK34" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:47</t>
+          <t>2026-10-12 13:49:50</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="AK35" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -6094,7 +6094,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:47</t>
+          <t>2026-10-12 13:49:50</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="AK36" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -6260,7 +6260,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -6279,7 +6279,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:48</t>
+          <t>2026-10-12 13:49:50</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -6410,7 +6410,7 @@
       </c>
       <c r="AK37" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -6426,31 +6426,31 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>브레이커즈</t>
+          <t>개집사</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=841810&amp;tab=fri</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=828292&amp;tab=fri</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>841810</t>
+          <t>828292</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:48</t>
+          <t>2026-10-12 13:49:50</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>JDL</t>
+          <t>고추참치</t>
         </is>
       </c>
       <c r="I38" t="b">
@@ -6481,21 +6481,21 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>브레이커즈</t>
+          <t>개집사</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>브레이커즈 (총 88화/미완결)</t>
+          <t>개집사 (총 203화/미완결)</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>총 88화/미완결</t>
+          <t>총 203화/미완결</t>
         </is>
       </c>
       <c r="R38" t="n">
-        <v>88</v>
+        <v>203</v>
       </c>
       <c r="S38" t="inlineStr">
         <is>
@@ -6504,21 +6504,187 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>평점 9.7 | JDL, 취룡 뚱또 | 2026.06.01. | 총88화/미완결 | 84화 무료</t>
+          <t>평점 10.0 | 고추참치 고추참치 | 2026.06.08. | 총203화/미완결 | 198화 무료</t>
         </is>
       </c>
       <c r="U38" t="inlineStr"/>
       <c r="V38" t="inlineStr">
         <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=11371316</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>11371316</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>개집사 (총 203화/미완결)
+평점
+10.0 | 고추참치 고추참치 | 2026.06.08. | 총203화/미완결 | 198화 무료
+출근도 퇴근도 없는 똑같은 일상의 작가…눈치채지 못한 사이 작가의 삶에 다이나믹한 소재를 주는 두 존재가 있었는데…! 작지만 자존감 만큼은 하늘 같은 말티즈, 덩칫값못하는 진도 믹스 아가씨들을 모시는 집사&amp;작가의 삶</t>
+        </is>
+      </c>
+      <c r="Y38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>145</v>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>title_contains,author_exact_or_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>first_non_compilation_numeric_download</t>
+        </is>
+      </c>
+      <c r="AE38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>59.2만</t>
+        </is>
+      </c>
+      <c r="AG38" t="n">
+        <v>592000</v>
+      </c>
+      <c r="AH38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>fri</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>금</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>59</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>브레이커즈</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=841810&amp;tab=fri</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>841810</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2026-10-12 13:49:50</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>JDL</t>
+        </is>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>화, 금 연재</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>tue,fri</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>tue,fri</t>
+        </is>
+      </c>
+      <c r="N39" t="n">
+        <v>1</v>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>브레이커즈</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>브레이커즈 (총 88화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>총 88화/미완결</t>
+        </is>
+      </c>
+      <c r="R39" t="n">
+        <v>88</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>평점 9.7 | JDL, 취룡 뚱또 | 2026.06.01. | 총88화/미완결 | 84화 무료</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="inlineStr">
+        <is>
           <t>https://series.naver.com/comic/detail.series?productNo=13011302</t>
         </is>
       </c>
-      <c r="W38" t="inlineStr">
+      <c r="W39" t="inlineStr">
         <is>
           <t>13011302</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
+      <c r="X39" t="inlineStr">
         <is>
           <t>브레이커즈 (총 88화/미완결)
 평점
@@ -6526,172 +6692,6 @@
 '주인공'은 즐겨하던 게임의 리메이크판인 &lt;나이트 사가:re&gt;를 플레이하던 중,게임 속으로 끌려들어 간다.그런데 무언가 이상하다.&lt;나이트 사가:re&gt;에서 플레이어블 캐릭터는 인간 편의 로크, 마계 편의 제피르뿐.그러나 정신..</t>
         </is>
       </c>
-      <c r="Y38" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z38" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>145</v>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>title_contains,author_exact_or_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>matched</t>
-        </is>
-      </c>
-      <c r="AD38" t="inlineStr">
-        <is>
-          <t>first_non_compilation_numeric_download</t>
-        </is>
-      </c>
-      <c r="AE38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF38" t="inlineStr">
-        <is>
-          <t>46.5만</t>
-        </is>
-      </c>
-      <c r="AG38" t="n">
-        <v>465000</v>
-      </c>
-      <c r="AH38" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AI38" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>2026-10-05 14:23:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>fri</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>금</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>58</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>개집사</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=828292&amp;tab=fri</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>828292</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>2026-10-05 13:35:48</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>고추참치</t>
-        </is>
-      </c>
-      <c r="I39" t="b">
-        <v>0</v>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>화, 금 연재</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>tue,fri</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>tue,fri</t>
-        </is>
-      </c>
-      <c r="N39" t="n">
-        <v>1</v>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>개집사</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>개집사 (총 203화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>총 203화/미완결</t>
-        </is>
-      </c>
-      <c r="R39" t="n">
-        <v>203</v>
-      </c>
-      <c r="S39" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T39" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 고추참치 고추참치 | 2026.06.08. | 총203화/미완결 | 198화 무료</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=11371316</t>
-        </is>
-      </c>
-      <c r="W39" t="inlineStr">
-        <is>
-          <t>11371316</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>개집사 (총 203화/미완결)
-평점
-10.0 | 고추참치 고추참치 | 2026.06.08. | 총203화/미완결 | 198화 무료
-출근도 퇴근도 없는 똑같은 일상의 작가…눈치채지 못한 사이 작가의 삶에 다이나믹한 소재를 주는 두 존재가 있었는데…! 작지만 자존감 만큼은 하늘 같은 말티즈, 덩칫값못하는 진도 믹스 아가씨들을 모시는 집사&amp;작가의 삶</t>
-        </is>
-      </c>
       <c r="Y39" t="b">
         <v>0</v>
       </c>
@@ -6721,11 +6721,11 @@
       </c>
       <c r="AF39" t="inlineStr">
         <is>
-          <t>59.2만</t>
+          <t>46.5만</t>
         </is>
       </c>
       <c r="AG39" t="n">
-        <v>592000</v>
+        <v>465000</v>
       </c>
       <c r="AH39" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
       </c>
       <c r="AK39" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -6777,7 +6777,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:51</t>
+          <t>2026-10-12 13:49:52</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="AK40" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -6947,7 +6947,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:51</t>
+          <t>2026-10-12 13:49:52</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -7078,7 +7078,7 @@
       </c>
       <c r="AK41" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -7113,7 +7113,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:51</t>
+          <t>2026-10-12 13:49:53</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -7244,7 +7244,7 @@
       </c>
       <c r="AK42" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -7260,7 +7260,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -7279,7 +7279,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:52</t>
+          <t>2026-10-12 13:49:53</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -7410,7 +7410,7 @@
       </c>
       <c r="AK43" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -7426,31 +7426,31 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>마님이네 미국 시골집 이야기</t>
+          <t>사회초년캣</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=814048&amp;tab=sat</t>
+          <t>https://comic.naver.com/webtoon/list?titleId=850237&amp;tab=sat</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>814048</t>
+          <t>850237</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:52</t>
+          <t>2026-10-12 13:49:53</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>마님</t>
+          <t>잇선</t>
         </is>
       </c>
       <c r="I44" t="b">
@@ -7463,17 +7463,17 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>수, 토 연재</t>
+          <t>목, 토 연재</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>thu,sat</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>wed,sat</t>
+          <t>thu,sat</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7481,21 +7481,21 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>마님이네 미국 시골집 이야기</t>
+          <t>사회초년캣</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>마님이네 미국 시골집 이야기 (총 288화/미완결)</t>
+          <t>사회초년캣 (총 15화/미완결)</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>총 288화/미완결</t>
+          <t>총 15화/미완결</t>
         </is>
       </c>
       <c r="R44" t="n">
-        <v>288</v>
+        <v>15</v>
       </c>
       <c r="S44" t="inlineStr">
         <is>
@@ -7504,21 +7504,187 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>평점 8.9 | 마님 마님 | 2026.06.05. | 총288화/미완결 | 285화 무료</t>
+          <t>평점 10.0 | 잇선 잇선 | 2026.06.05. | 총15화/미완결 | 10화 무료</t>
         </is>
       </c>
       <c r="U44" t="inlineStr"/>
       <c r="V44" t="inlineStr">
         <is>
+          <t>https://series.naver.com/comic/detail.series?productNo=14110481</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>14110481</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>사회초년캣 (총 15화/미완결)
+평점
+10.0 | 잇선 잇선 | 2026.06.05. | 총15화/미완결 | 10화 무료
+냐냐냐냥 냐냐냐냐냥냐냐냥냐냐냥 냐냐냥 냐냐냥냐냐냥(인간 사회에 적응해 볼게요)</t>
+        </is>
+      </c>
+      <c r="Y44" t="b">
+        <v>0</v>
+      </c>
+      <c r="Z44" t="b">
+        <v>1</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>145</v>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>title_contains,author_exact_or_contains,bonus_total_episode_info,bonus_rank_1</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>matched</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>first_non_compilation_numeric_download</t>
+        </is>
+      </c>
+      <c r="AE44" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>2.8만</t>
+        </is>
+      </c>
+      <c r="AG44" t="n">
+        <v>28000</v>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>reused_existing_product_no</t>
+        </is>
+      </c>
+      <c r="AJ44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AK44" t="inlineStr">
+        <is>
+          <t>2026-10-12 14:31:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>sat</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>토</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>52</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>마님이네 미국 시골집 이야기</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>https://comic.naver.com/webtoon/list?titleId=814048&amp;tab=sat</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>814048</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>2026-10-12 13:49:53</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>마님</t>
+        </is>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>수, 토 연재</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>wed,sat</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>1</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>마님이네 미국 시골집 이야기</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>마님이네 미국 시골집 이야기 (총 288화/미완결)</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>총 288화/미완결</t>
+        </is>
+      </c>
+      <c r="R45" t="n">
+        <v>288</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>미완결</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>평점 8.9 | 마님 마님 | 2026.06.05. | 총288화/미완결 | 285화 무료</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr"/>
+      <c r="V45" t="inlineStr">
+        <is>
           <t>https://series.naver.com/comic/detail.series?productNo=10056128</t>
         </is>
       </c>
-      <c r="W44" t="inlineStr">
+      <c r="W45" t="inlineStr">
         <is>
           <t>10056128</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
+      <c r="X45" t="inlineStr">
         <is>
           <t>마님이네 미국 시골집 이야기 (총 288화/미완결)
 평점
@@ -7526,172 +7692,6 @@
 마님♡올리버쌤♡체리 가족이 찾아왔습니다!미국 남자 올리버와, 토종 한국인 마님, 그리고 사랑스러운 딸 체리와 다섯 마리 반려 동물까지.하루종일 육아하고 털 청소하느라 바쁘지만, 그래도 하하 호호 행복한 미국 시골집 ..</t>
         </is>
       </c>
-      <c r="Y44" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z44" t="b">
-        <v>1</v>
-      </c>
-      <c r="AA44" t="n">
-        <v>145</v>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>title_contains,author_exact_or_contains,bonus_total_episode_info,bonus_rank_1</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>matched</t>
-        </is>
-      </c>
-      <c r="AD44" t="inlineStr">
-        <is>
-          <t>first_non_compilation_numeric_download</t>
-        </is>
-      </c>
-      <c r="AE44" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF44" t="inlineStr">
-        <is>
-          <t>71.5만</t>
-        </is>
-      </c>
-      <c r="AG44" t="n">
-        <v>715000</v>
-      </c>
-      <c r="AH44" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="AI44" t="inlineStr">
-        <is>
-          <t>reused_existing_product_no</t>
-        </is>
-      </c>
-      <c r="AJ44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>2026-10-05 14:23:55</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>sat</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>토</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>52</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>사회초년캣</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>https://comic.naver.com/webtoon/list?titleId=850237&amp;tab=sat</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>850237</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>2026-10-05 13:35:52</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>잇선</t>
-        </is>
-      </c>
-      <c r="I45" t="b">
-        <v>0</v>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>목, 토 연재</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>thu,sat</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>thu,sat</t>
-        </is>
-      </c>
-      <c r="N45" t="n">
-        <v>1</v>
-      </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>사회초년캣</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
-        <is>
-          <t>사회초년캣 (총 15화/미완결)</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>총 15화/미완결</t>
-        </is>
-      </c>
-      <c r="R45" t="n">
-        <v>15</v>
-      </c>
-      <c r="S45" t="inlineStr">
-        <is>
-          <t>미완결</t>
-        </is>
-      </c>
-      <c r="T45" t="inlineStr">
-        <is>
-          <t>평점 10.0 | 잇선 잇선 | 2026.06.05. | 총15화/미완결 | 10화 무료</t>
-        </is>
-      </c>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr">
-        <is>
-          <t>https://series.naver.com/comic/detail.series?productNo=14110481</t>
-        </is>
-      </c>
-      <c r="W45" t="inlineStr">
-        <is>
-          <t>14110481</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>사회초년캣 (총 15화/미완결)
-평점
-10.0 | 잇선 잇선 | 2026.06.05. | 총15화/미완결 | 10화 무료
-냐냐냐냥 냐냐냐냐냥냐냐냥냐냐냥 냐냐냥 냐냐냥냐냐냥(인간 사회에 적응해 볼게요)</t>
-        </is>
-      </c>
       <c r="Y45" t="b">
         <v>0</v>
       </c>
@@ -7721,11 +7721,11 @@
       </c>
       <c r="AF45" t="inlineStr">
         <is>
-          <t>2.8만</t>
+          <t>71.5만</t>
         </is>
       </c>
       <c r="AG45" t="n">
-        <v>28000</v>
+        <v>715000</v>
       </c>
       <c r="AH45" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
       </c>
       <c r="AK45" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -7758,7 +7758,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:52</t>
+          <t>2026-10-12 13:49:53</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7908,7 +7908,7 @@
       </c>
       <c r="AK46" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:52</t>
+          <t>2026-10-12 13:49:54</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -8074,7 +8074,7 @@
       </c>
       <c r="AK47" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -8109,7 +8109,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:54</t>
+          <t>2026-10-12 13:49:55</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="AK48" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -8275,7 +8275,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:54</t>
+          <t>2026-10-12 13:49:55</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="AK49" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -8412,7 +8412,7 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -8431,7 +8431,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:55</t>
+          <t>2026-10-12 13:49:56</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -8562,7 +8562,7 @@
       </c>
       <c r="AK50" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8578,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -8597,7 +8597,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:55</t>
+          <t>2026-10-12 13:49:56</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -8728,7 +8728,7 @@
       </c>
       <c r="AK51" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -8744,7 +8744,7 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:55</t>
+          <t>2026-10-12 13:49:56</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8894,7 +8894,7 @@
       </c>
       <c r="AK52" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -8910,7 +8910,7 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -8929,7 +8929,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:55</t>
+          <t>2026-10-12 13:49:57</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="AK53" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>2026-10-05 13:35:57</t>
+          <t>2026-10-12 13:49:58</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -9177,7 +9177,7 @@
       </c>
       <c r="AK54" t="inlineStr">
         <is>
-          <t>2026-10-05 14:23:55</t>
+          <t>2026-10-12 14:31:25</t>
         </is>
       </c>
     </row>
